--- a/data/trans_orig/P17E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24991</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>27892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>47878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37373</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>67724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89616</t>
+          <t>87710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>75,87%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28975</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>49871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>41881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>68300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63625</t>
+          <t>64039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79739</t>
+          <t>79639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>82380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103276</t>
+          <t>102967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151587</t>
+          <t>153015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178186</t>
+          <t>179434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41687</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51581</t>
+          <t>51566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82275</t>
+          <t>83200</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94812</t>
+          <t>94796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129215</t>
+          <t>129184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144388</t>
+          <t>144136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24316</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>47729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95605</t>
+          <t>94291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110751</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134404</t>
+          <t>136319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>153713</t>
+          <t>154641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15867</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33112</t>
+          <t>33163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>32197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>67189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87727</t>
+          <t>87676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104972</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>33017</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78482</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101510</t>
+          <t>102277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118543</t>
+          <t>118500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22485</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47411</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75518</t>
+          <t>74788</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106039</t>
+          <t>105843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124342</t>
+          <t>124681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171930</t>
+          <t>171042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>192579</t>
+          <t>191842</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282801</t>
+          <t>283531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>310908</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>50505</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48585</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78806</t>
+          <t>78280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83955</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121946</t>
+          <t>121205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130456</t>
+          <t>129542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>152673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172936</t>
+          <t>173462</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203157</t>
+          <t>201795</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>309843</t>
+          <t>310584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347834</t>
+          <t>346282</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>112176</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151915</t>
+          <t>151942</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>182290</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>238596</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>307022</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>375223</t>
+          <t>373086</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>507387</t>
+          <t>507360</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>547126</t>
+          <t>548923</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>809774</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>866080</t>
+          <t>861914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1332449</t>
+          <t>1334586</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1398368</t>
+          <t>1400650</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2012 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21910</t>
+          <t>21982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43329</t>
+          <t>43914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50864</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73220</t>
+          <t>72922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88788</t>
+          <t>87961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>113551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135555</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>32321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52397</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74853</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93818</t>
+          <t>94700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121517</t>
+          <t>122046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139865</t>
+          <t>139879</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205691</t>
+          <t>204101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>230103</t>
+          <t>229589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31144</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>26603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49256</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61501</t>
+          <t>61487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77203</t>
+          <t>76705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112161</t>
+          <t>111595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130641</t>
+          <t>130032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180377</t>
+          <t>180720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203078</t>
+          <t>203030</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>33149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>52307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46225</t>
+          <t>46160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>60974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79754</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97058</t>
+          <t>97214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131677</t>
+          <t>132395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155617</t>
+          <t>154561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,68%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>28144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36335</t>
+          <t>36744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>62896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>78701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105292</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123657</t>
+          <t>123044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25175</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53864</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84168</t>
+          <t>83728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99516</t>
+          <t>99681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143910</t>
+          <t>142965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165672</t>
+          <t>165054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48287</t>
+          <t>49031</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67477</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73069</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107813</t>
+          <t>107346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119757</t>
+          <t>119013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141142</t>
+          <t>140988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154630</t>
+          <t>155048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180676</t>
+          <t>180982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282338</t>
+          <t>282805</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317082</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>42191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>30236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54013</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59691</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>91332</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113105</t>
+          <t>114389</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134486</t>
+          <t>134837</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169094</t>
+          <t>168779</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192378</t>
+          <t>192871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289478</t>
+          <t>288355</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>319996</t>
+          <t>320256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139462</t>
+          <t>141433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187798</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>188703</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>240049</t>
+          <t>241434</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>341123</t>
+          <t>341360</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>415989</t>
+          <t>409593</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>592342</t>
+          <t>592148</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>640678</t>
+          <t>638707</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>913415</t>
+          <t>912030</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>965846</t>
+          <t>964761</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1517615</t>
+          <t>1524011</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1592481</t>
+          <t>1592244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>29419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>40354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56027</t>
+          <t>55226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>64569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80324</t>
+          <t>79884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108461</t>
+          <t>109359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131672</t>
+          <t>132042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,78%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>29383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46853</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69232</t>
+          <t>70175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80572</t>
+          <t>81284</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97569</t>
+          <t>97218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134910</t>
+          <t>135354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157065</t>
+          <t>157480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223198</t>
+          <t>222255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250636</t>
+          <t>250336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>20025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>32789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68132</t>
+          <t>67328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>84228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97702</t>
+          <t>97489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145132</t>
+          <t>145830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162237</t>
+          <t>162890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62457</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>62165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77752</t>
+          <t>77622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94297</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116293</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161279</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187840</t>
+          <t>188490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36925</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47719</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>62408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76218</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40628</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89120</t>
+          <t>88950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101898</t>
+          <t>101429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>101423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117712</t>
+          <t>118157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196654</t>
+          <t>196144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216940</t>
+          <t>217504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41917</t>
+          <t>42785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>52314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57495</t>
+          <t>55642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89044</t>
+          <t>88273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108111</t>
+          <t>107243</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129096</t>
+          <t>129342</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134071</t>
+          <t>134086</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157467</t>
+          <t>156372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247384</t>
+          <t>248155</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278933</t>
+          <t>280786</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40488</t>
+          <t>39284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67110</t>
+          <t>68420</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80454</t>
+          <t>79941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116291</t>
+          <t>116964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166391</t>
+          <t>167349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191466</t>
+          <t>191577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>212638</t>
+          <t>211328</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239260</t>
+          <t>240464</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>387725</t>
+          <t>387052</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>423562</t>
+          <t>424075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133518</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178957</t>
+          <t>181224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>196249</t>
+          <t>193700</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>251235</t>
+          <t>247380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>341478</t>
+          <t>343729</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>411442</t>
+          <t>418287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>672677</t>
+          <t>670410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>718116</t>
+          <t>718216</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>913085</t>
+          <t>916940</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>968071</t>
+          <t>970620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1604511</t>
+          <t>1597666</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1674475</t>
+          <t>1672224</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>42309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>50344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>62833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59895</t>
+          <t>60268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103025</t>
+          <t>103144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120548</t>
+          <t>120585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36494</t>
+          <t>37037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>34883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57094</t>
+          <t>57192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63764</t>
+          <t>63651</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70784</t>
+          <t>70835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84249</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>121698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143653</t>
+          <t>144007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29292</t>
+          <t>29363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28857</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47987</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39756</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>53762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46488</t>
+          <t>46417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91099</t>
+          <t>91106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110229</t>
+          <t>110184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16560</t>
+          <t>17453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85583</t>
+          <t>84704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53704</t>
+          <t>52811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111505</t>
+          <t>113163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159309</t>
+          <t>159694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154527</t>
+          <t>155406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214497</t>
+          <t>218485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>5921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43435</t>
+          <t>43488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>36649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>44472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37253</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>47938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74576</t>
+          <t>74624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89645</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52695</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46468</t>
+          <t>47486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>71290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82646</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115317</t>
+          <t>112899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>89035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110979</t>
+          <t>111625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125319</t>
+          <t>124512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149334</t>
+          <t>148316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220503</t>
+          <t>222921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>253174</t>
+          <t>255756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34154</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56138</t>
+          <t>56221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113250</t>
+          <t>112773</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129544</t>
+          <t>129224</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162149</t>
+          <t>161880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>177448</t>
+          <t>178059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281376</t>
+          <t>281293</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>303360</t>
+          <t>304077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132227</t>
+          <t>132158</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>174862</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>144797</t>
+          <t>149534</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220225</t>
+          <t>219688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>290101</t>
+          <t>295990</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>382749</t>
+          <t>383975</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>463966</t>
+          <t>460604</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>506601</t>
+          <t>506670</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>675612</t>
+          <t>676149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>751040</t>
+          <t>746303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1151916</t>
+          <t>1150690</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1244564</t>
+          <t>1238675</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>28242</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>47476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24972</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67724</t>
+          <t>68126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87710</t>
+          <t>88299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49871</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68300</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64039</t>
+          <t>62925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79639</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>83482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102967</t>
+          <t>103240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153015</t>
+          <t>151546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179434</t>
+          <t>179149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51566</t>
+          <t>51443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83200</t>
+          <t>82947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94796</t>
+          <t>94944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129184</t>
+          <t>128938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144136</t>
+          <t>144268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>47656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94291</t>
+          <t>94648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109746</t>
+          <t>109799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136319</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154641</t>
+          <t>154439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33163</t>
+          <t>34227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67189</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87676</t>
+          <t>86612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105375</t>
+          <t>104589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3646</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33017</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42237</t>
+          <t>42198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>64863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102277</t>
+          <t>103206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118500</t>
+          <t>119468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>46827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>74929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105843</t>
+          <t>105862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>125179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171042</t>
+          <t>170303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191842</t>
+          <t>192026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>283531</t>
+          <t>283390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>311699</t>
+          <t>311492</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50505</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>50706</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78280</t>
+          <t>79358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85507</t>
+          <t>84349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121205</t>
+          <t>121283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129542</t>
+          <t>130269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>152088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173462</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201795</t>
+          <t>201036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>310584</t>
+          <t>310506</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>346282</t>
+          <t>347440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151942</t>
+          <t>151224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>187574</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>238596</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>307022</t>
+          <t>306808</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>373086</t>
+          <t>373335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>507360</t>
+          <t>508078</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>548923</t>
+          <t>548270</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>809774</t>
+          <t>810720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1334586</t>
+          <t>1334337</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1400650</t>
+          <t>1400864</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>35443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>50281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>73351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87961</t>
+          <t>88629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113551</t>
+          <t>113502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>134707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32321</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53987</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76870</t>
+          <t>76352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94700</t>
+          <t>93997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122046</t>
+          <t>121697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139879</t>
+          <t>139874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204101</t>
+          <t>205145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229589</t>
+          <t>230574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>49229</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61487</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76705</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111595</t>
+          <t>112171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130032</t>
+          <t>130530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180720</t>
+          <t>180404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203030</t>
+          <t>203548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24716</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>16241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52307</t>
+          <t>52064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46160</t>
+          <t>47399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60974</t>
+          <t>61393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80676</t>
+          <t>79590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97214</t>
+          <t>97584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132395</t>
+          <t>132638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154561</t>
+          <t>154557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39003</t>
+          <t>39149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36744</t>
+          <t>36622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62896</t>
+          <t>62676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78701</t>
+          <t>78909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104029</t>
+          <t>103883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123044</t>
+          <t>122780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26284</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83728</t>
+          <t>85021</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99681</t>
+          <t>99812</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142965</t>
+          <t>143519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165054</t>
+          <t>165618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,78%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>41852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>68319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74718</t>
+          <t>73255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107346</t>
+          <t>108424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119013</t>
+          <t>120713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140988</t>
+          <t>142209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>155048</t>
+          <t>153788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180982</t>
+          <t>180255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282805</t>
+          <t>281727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315433</t>
+          <t>316896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30236</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59431</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91332</t>
+          <t>91313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114389</t>
+          <t>112894</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168779</t>
+          <t>169390</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>192871</t>
+          <t>193138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288355</t>
+          <t>288374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320256</t>
+          <t>321277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141433</t>
+          <t>142425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187992</t>
+          <t>187611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>188703</t>
+          <t>188036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>241434</t>
+          <t>241797</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>341360</t>
+          <t>339911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>409593</t>
+          <t>413673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>592148</t>
+          <t>592529</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>638707</t>
+          <t>637715</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>912030</t>
+          <t>911667</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>964761</t>
+          <t>965428</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1524011</t>
+          <t>1519931</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1592244</t>
+          <t>1593693</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>27935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52102</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>39827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55226</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64569</t>
+          <t>63997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79884</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109359</t>
+          <t>108477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132042</t>
+          <t>130959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>45857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70175</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81284</t>
+          <t>81069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97218</t>
+          <t>98059</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135354</t>
+          <t>135906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>157480</t>
+          <t>157069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222255</t>
+          <t>223746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>250336</t>
+          <t>250600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32789</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55272</t>
+          <t>56031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84228</t>
+          <t>84990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97489</t>
+          <t>97677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>145053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162890</t>
+          <t>162364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21901</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35246</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62974</t>
+          <t>61830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62165</t>
+          <t>62296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93197</t>
+          <t>94276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114429</t>
+          <t>114977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160762</t>
+          <t>161906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188490</t>
+          <t>187913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62408</t>
+          <t>62675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75895</t>
+          <t>76271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>20659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>41282</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88950</t>
+          <t>88511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>101287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101423</t>
+          <t>101636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118157</t>
+          <t>118806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196144</t>
+          <t>196000</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>217504</t>
+          <t>216623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42785</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>30315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>53205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>56811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88273</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107243</t>
+          <t>107551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129342</t>
+          <t>129533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134086</t>
+          <t>133195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156372</t>
+          <t>156085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248155</t>
+          <t>249580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280786</t>
+          <t>279617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>58331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>68316</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79941</t>
+          <t>79862</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116964</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167349</t>
+          <t>165937</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191577</t>
+          <t>191075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>211328</t>
+          <t>211432</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>240464</t>
+          <t>239761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>387052</t>
+          <t>385212</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>424075</t>
+          <t>424154</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>133418</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>181224</t>
+          <t>180688</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193700</t>
+          <t>193667</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247380</t>
+          <t>250617</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>343729</t>
+          <t>341072</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>418287</t>
+          <t>415502</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>670410</t>
+          <t>670946</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>718216</t>
+          <t>718290</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>916940</t>
+          <t>913703</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>970620</t>
+          <t>970653</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1597666</t>
+          <t>1600451</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1672224</t>
+          <t>1674881</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>33248</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42309</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57398</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50344</t>
+          <t>45544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62833</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>60693</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48229</t>
+          <t>54313</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60268</t>
+          <t>66004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112131</t>
+          <t>113324</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103144</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120585</t>
+          <t>121076</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37037</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,67 +11075,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>12880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25818</t>
+          <t>27600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>47136</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>35030</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>58766</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>25,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>18,81%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>45443</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>34883</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>57192</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54977</t>
+          <t>57284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,67 +11188,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78470</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70835</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>88445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>139076</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>127446</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>151182</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>68,44%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>81,19%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>133447</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>121698</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>144007</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>74,6%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>68,03%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82237</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82237</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82237</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>186212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29363</t>
+          <t>29407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40451</t>
+          <t>41696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>54365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54047</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>48854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>62587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>101532</t>
+          <t>104533</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91106</t>
+          <t>93309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110184</t>
+          <t>112704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>139086</t>
+          <t>142311</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139086</t>
+          <t>142311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139086</t>
+          <t>142311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>66116</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84704</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45559</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52811</t>
+          <t>64137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138309</t>
+          <t>76782</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113163</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159694</t>
+          <t>85941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>183869</t>
+          <t>131243</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155406</t>
+          <t>116680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218485</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>240110</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>240110</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>240110</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7707</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>25749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>27946</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21489</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36649</t>
+          <t>35829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>38698</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34304</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>42997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42750</t>
+          <t>44178</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36356</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>49326</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>82876</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74624</t>
+          <t>74993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110822</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110822</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110822</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>44302</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50984</t>
+          <t>58593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>57692</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>60386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71290</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>116434</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>98871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112899</t>
+          <t>134132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>101339</t>
+          <t>115942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89035</t>
+          <t>101651</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111625</t>
+          <t>128205</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>138110</t>
+          <t>169762</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124512</t>
+          <t>155946</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148316</t>
+          <t>181508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>239448</t>
+          <t>285704</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>222921</t>
+          <t>268006</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>255756</t>
+          <t>303267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>160244</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>160244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>160244</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>195802</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>195802</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195802</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>335820</t>
+          <t>402138</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>335820</t>
+          <t>402138</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>335820</t>
+          <t>402138</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44270</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56221</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>122420</t>
+          <t>136297</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112773</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129224</t>
+          <t>144313</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>170824</t>
+          <t>191177</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161880</t>
+          <t>181182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178059</t>
+          <t>199261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>293244</t>
+          <t>327474</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281293</t>
+          <t>313014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>304077</t>
+          <t>338862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>195837</t>
+          <t>220419</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>195837</t>
+          <t>220419</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>195837</t>
+          <t>220419</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>337514</t>
+          <t>379350</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>337514</t>
+          <t>379350</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>337514</t>
+          <t>379350</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>153801</t>
+          <t>167311</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>146418</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178224</t>
+          <t>194015</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>193591</t>
+          <t>219793</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149534</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>219688</t>
+          <t>243175</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>347392</t>
+          <t>387104</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295990</t>
+          <t>355774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>383975</t>
+          <t>422041</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>520658</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>460604</t>
+          <t>493954</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>506670</t>
+          <t>541551</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>702246</t>
+          <t>706040</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>676149</t>
+          <t>682658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>746303</t>
+          <t>729518</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1187273</t>
+          <t>1226698</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1150690</t>
+          <t>1191761</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1238675</t>
+          <t>1258028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>638828</t>
+          <t>687969</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>895837</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1613802</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P17E-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Provincia-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2203,7 +2203,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2889,7 +2889,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -5869,7 +5869,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7477,7 +7477,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7820,7 +7820,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -8163,7 +8163,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8849,7 +8849,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -11143,7 +11143,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -11829,7 +11829,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -12172,7 +12172,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -12515,7 +12515,7 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -13201,7 +13201,7 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
